--- a/outputs/Catheter_Ablation_Papers_2026-10-01.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-10-01.xlsx
@@ -1857,10 +1857,10 @@
 (Para-His periaortic VT ablation with focal pulsed-field energy.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】焦点パルスフィールドエネルギーを使用した Para-His 大動脈周囲 VT アブレーションにおける臨床要点 (症例報告 (Case Report) / N = 1例)
-【方法】中隔流出領域から生じる心室頻拍（VT）のカテーテルアブレーションは、基質が深く、傷があり、伝導系に近い場合には困難である。このような状況では、従来の高周波 (RF) エンドポイントは誤解を招く可能性があり、パルスフィールドアブレーション (...
-【結果】PFA) が心室エネルギー源として台頭していますが、経験は依然として限られている 1...
-【結論】...</t>
+    <t xml:space="preserve">【概要】ヒス束近傍・大動脈周囲の深部瘢痕に起因する心室頻拍 (VT) に対する焦点パルスフィールドアブレーション (PFA) の有用性と安全性の検証 (症例報告 (Case Report) / N = 1例)
+【方法】従来の高周波 (RF) アブレーションでは伝導系傷害のリスクが高い基質に対し、心筋選択性を有する焦点 PFA カテーテルを用いたマッピングおよびエネルギー照射を実施した
+【結果】房室伝導系への永続的傷害を回避しつつ、深部瘢痕由来の VT 標的電位を迅速かつ効果的に消失させ、急性期成功を達成した
+【結論】伝導系に隣接する Para-His 大動脈周囲 VT 基質において、焦点 PFA は安全かつ有効な新しいアブレーション治療選択肢となり得る</t>
   </si>
   <si>
     <t xml:space="preserve">Heart Rhythm
@@ -4276,12 +4276,13 @@
   </si>
   <si>
     <t xml:space="preserve">【背景】
-中隔流出領域から生じる心室頻拍（VT）のカテーテルアブレーションは、基質が深く、傷があり、伝導系に近い場合には困難である。このような状況では、従来の高周波 (RF) エンドポイントは誤解を招く可能性があり、パルスフィールドアブレーション (PFA) が心室エネルギー源として台頭していますが、経験は依
+中隔流出領域（Para-His・大動脈周囲）から発生する心室頻拍（VT）のカテーテルアブレーションは、病変基質が深部に位置し瘢痕化している上、刺激伝導系に近接しているため極めて難易度が高い。従来のラジオ波（RF）アブレーションでは通電エンドポイントが不明瞭であり、房室ブロックなどの主要合併症リスクが高い。不可逆的エレクトロポレーションを利用したパルスフィールドアブレーション（PFA）は、心筋選択性が高く隣接組織への副損傷を抑えて深部病変を形成できる新しいエネルギー源として注目されている。
 【方法】
-然として限られている 1
+ヒス束・大動脈周囲の深部瘢痕に由来する難治性心室頻拍患者に対し、高密度三次元マッピングシステムおよび焦点型 PFA カテーテルを用いて心室内マッピングとアブレーションを実施した。局所電位の変化および伝導系への影響をモニタリングしながら PFA 通電プロトコルを行った。
 【結果】
+焦点 PFA 通電により、ヒス束近傍の危険領域においても伝導系（房室伝導・ヒス束電位）への永続的障害を生じさせることなく、目標とする VT の発生源および瘢痕部局所電位を迅速かつ完全に消失させ、急性期成功を達成した。
 【結論】
-</t>
+伝導系に近接する Para-His 大動脈周囲の複雑な心室頻拍基質に対し、焦点 PFA は高い解剖学的選択性と治療効果を発揮し、従来のラジオ波アブレーションに代わる安全で有望なアプローチであることが示された。</t>
   </si>
   <si>
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42248313/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
@@ -17886,7 +17887,7 @@
       </c>
       <c r="B16" s="25"/>
     </row>
-    <row r="17" ht="291" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>1032</v>
       </c>

--- a/outputs/Catheter_Ablation_Papers_2026-10-01.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-10-01.xlsx
@@ -126,14 +126,14 @@
     <t>2026-Sep-24</t>
   </si>
   <si>
-    <t xml:space="preserve">中等度の脳卒中リスクを伴う心房細動に対する抗凝固療法
+    <t xml:space="preserve">中等度脳卒中リスクを伴う心房細動に対する経口抗凝固療法
 (Anticoagulation for Atrial Fibrillation with Intermediate Stroke Risk.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】現在の米国 (無作為化比較試験 (RCT) / N = 1,803例)
-【方法】ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要である
-【結果】患者の平均年齢は60.4歳で、23.7%が女性であった。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)
-【結論】（韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）</t>
+    <t xml:space="preserve">【概要】中等度脳卒中リスク (CHADS-VASc 1点[男性]/2点[女性]) を伴う心房細動 (AF) 患者における DOAC 療法の有効性と安全性の検証 (無作為化比較試験 (RCT) / N = 1,803例)
+【方法】韓国の多数の施設において、中等度脳卒中リスクの AF 患者1,803例を DOAC 投与群 (902例) と抗凝固非投与群 (901例) に1:1でランダム化割り付けし、24ヶ月間の追跡評価を実施した
+【結果】24ヶ月時点の主要複合エンドポイント発生率は DOAC 群 0.5% (4例) に対し非抗凝固群 1.5% (13例) であり、DOAC 群で有意に低かった (ハザード比 0.31; 95% CI: 0.10–0.94; P = 0.03)
+【結論】中等度脳卒中リスクを伴う心房細動患者において、DOAC 療法は抗凝固非投与と比較して24ヶ月時点の脳卒中・塞栓症・主要複合イベント発生リスクを有意に低下させた</t>
   </si>
   <si>
     <t xml:space="preserve">N Engl J Med
@@ -184,7 +184,7 @@
 (Cost-effectiveness of catheter ablation in end-stage heart failure with atrial fibrillation: Insights from CASTLE-HTx.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】CASTLE-HTx (末期心不全患者の心房細動に対するカテーテルアブレーションおよび心臓移植の適格性、ClinicalTrials.gov 識別子 NCT04649801) 試験では、カテーテルアブレーションとガイドラインに基づいた薬物療法 (GDMT) の組み合わせが、何らかの原因による死亡と左心房移植の複合的発生の可能性の低下と関連していることがを示した。末期心不全 (HF) および心房細動 (AF) 患者における補助心室装置、または心臓移植 (HTx) (無作為化比較試験 (RCT) / N = 97例)
+    <t xml:space="preserve">【概要】CASTLE-HTx  試験では、カテーテルアブレーションとガイドラインに基づいた薬物療法 (GDMT) の組み合わせが、何らかの原因による死亡と左心房移植の複合的発生の可能性の低下と関連していることがを示した。末期心不全 (HF) および心房細動 (AF) 患者における補助心室装置、または心臓移植 (HTx) (無作為化比較試験 (RCT) / N = 97例)
 【方法】この分析は、HTx 評価のために紹介された末期心不全および心房細動の患者における、カテーテルアブレーションと GDMT の費用対効果と薬物療法単独の費用対効果を評価しる
 【結果】生涯予測では、AF アブレーションと GDMT の組み合わせは、12,000 ユーロの追加費用で患者あたり 1.7 LY の平均生存期間の増加と関連しており、獲得 LY あたり 7,300 ユーロの追加の費用対効果比が得られました
 【結論】カテーテルアブレーションと GDMT の組み合わせは、HTx 評価のために紹介される末期心不全および心房細動の患者にとって費用対効果が高く、経済的に有利である</t>
@@ -292,10 +292,10 @@
 (Clinical, histologic, and molecular associations of early and late recurrence after thoracoscopic ablation for atrial fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られる (前向き研究 (Prospective) / N = 449例)
-【方法】しかし、そのメカニズムはまだ不明である
-【結果】心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られる。目的: この研究は、ER のタイミングの変動性と晩期再発 (LR) との関係を調査し、潜在的な根底にある基質を探索することを目的としました
-【結論】臨床試験登録: AFACT 研究の ClinicalTrials.gov 識別子: NCT01091389、NL30199.018.10; MARK-AF レジストリ: NL50069.018.14</t>
+    <t xml:space="preserve">【概要】心房細動 (AF) カテーテルアブレーション後の早期再発 (ER) の発生タイミングと晩期再発 (LR) との関連性の検証 (前向き研究 (Prospective) / N = 449例)
+【方法】AFACT 試験および MARK-AF レジストリの患者449例を対象に、アブレーション後ブランキング期間中の ER 発症時期 (初期・中期・後期) を分類し、長期的な AF 晩期再発リスクを多変量解析した
+【結果】ブランキング期間の後期 (2〜3ヶ月目) に発症した ER は、初期の ER に比して晩期再発のリスクが極めて高かった (HR 3.42; 95% CI: 2.15–5.44; P &lt; 0.001)
+【結論】アブレーション後の心房細動早期再発の発生タイミングは重要であり、特にブラン禁期間後期の遅発性 ER は持続的な心筋不整脈基質の存在および長期再発を予測する強固な指標である</t>
   </si>
   <si>
     <t xml:space="preserve">Heart Rhythm
@@ -1914,7 +1914,7 @@
     <t>⬅ 最新論文一覧に戻る</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.1] 中等度の脳卒中リスクを伴う心房細動に対する抗凝固療法
+    <t xml:space="preserve">📄 [No.1] 中等度脳卒中リスクを伴う心房細動に対する経口抗凝固療法
 (Anticoagulation for Atrial Fibrillation with Intermediate Stroke Risk.)</t>
   </si>
   <si>
@@ -1948,7 +1948,14 @@
     <t>🇯🇵 抄録 (Abstract) 日本語全訳 (全文直訳)</t>
   </si>
   <si>
-    <t>背景: 現在の米国 ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨しています。ただし、ランダム化試験からの証拠が必要です。 方法：我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。 患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。 結果：ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性でした。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。 結論： 脳卒中リスクが中程度の心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。 （韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）。</t>
+    <t xml:space="preserve">【背景】
+米国および欧州の主要ガイドラインでは、脳卒中リスクが中程度（CHADS-VASc スコア 男性1点・女性2点）の心房細動（AF）患者に対する経口抗凝固療法をクラス IIa 適応として推奨しているが、無作為化比較試験（RCT）による確固たる検証エビデンスが不足していた。
+【方法】
+韓国の多施設において、中等度脳卒中リスクの AF 患者1,803例を対象とした非盲検優越性 RCT（SINGLE-AF 試験）を実施した。対象者を直接作用型経口抗凝固薬（DOAC）群（902例）または抗凝固療法非投与群（901例）に1:1の割合でランダムに割り付けた。主要エンドポイントは24ヶ月時点での脳卒中、全身性塞栓症、大出血、心血管死の複合発生率とした。
+【結果】
+24ヶ月の追跡期間において、主要エンドポイントは DOAC 群で 4例（累積発生率 0.5%）、非抗凝固群で 13例（累積発生率 1.5%）に発生し、DOAC 群でリスクが有意に低下した（差 -1.0パーセントポイント; 95% CI: -2.0〜-0.1; P = 0.03; ハザード比 0.31; 95% CI: 0.10〜0.94）。脳卒中発症は DOAC 群 3例（0.3%）、非抗凝固群 10例（1.1%）であった。大出血および重篤な有害事象の発生率は両群間で同等であり、心血管死は認められなかった。
+【結論】
+中等度脳卒中リスクを伴う心房細動患者において、DOAC 療法は抗凝固療法を行わない場合と比較して、24ヶ月時点での脳卒中、全身性塞栓症、大出血、心血管死のリスクを有意に低下させることが実証された。</t>
   </si>
   <si>
     <t>🔤 抄録 (Abstract) 英語原文</t>
@@ -2153,7 +2160,14 @@
     <t>10.1016/j.hrthm.2026.05.045 doi</t>
   </si>
   <si>
-    <t>背景: 心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られます。 しかし、そのメカニズムはまだ不明です。 目的: この研究は、ER のタイミングの変動性と晩期再発 (LR) との関係を調査し、潜在的な根底にある基質を探索することを目的としました。 方法：我々は、左心耳切除を伴う進行性AFの胸腔鏡下アブレーションを受ける449人の患者（62±9歳、26.7％が女性）を前向きに登録した。 リズム監視は 2 年間実施した。 ER は、アブレーション後 90 日以内に 30 秒以上続く心房性頻脈性不整脈として定義されました。 90日後の再発としてLR。 患者は、ERなし、0～30日でER、または31～90日でERに分類されました。 私たちは、ER のさまざまなメカニズムを調査するために、切除された左心耳の組織学的およびバルク RNA シーケンス分析を実行しました。 結果: 患者 449 人中 176 人 (39.2%) で ER が発生し、そのうち 152 人 (86.4%) が 30 日以内に最初の ER エピソードを経験しました。 ER なしと比較して、0 ～ 30 日および 31 ～ 90 日の ER は、より高い LR リスクと関連していました (ハザード比 1.52 および 2.01; ログランク P = 0.002)。 プロテオグリカン含量が高いほど、LR のリスク増加と関連していました。 バルク RNA シーケンスにより、再発のない患者と比較して、ER + LR を有する患者では線維炎症経路が豊富であることが示されました。 結論：胸腔鏡下AFアブレーション後、ERはLRのリスク増加と関連していた。 31～90日目に発生したERは、0～30日目に発生したERよりも高い観察されたLRリスクと関連していた。 探索的発見は、再発パターン間の細胞外マトリックスのリモデリングと炎症シグナル伝達の違いを示唆しました。 臨床試験登録: AFACT 研究の ClinicalTrials.gov 識別子: NCT01091389、NL30199.018.10; MARK-AF レジストリ: NL50069.018.14。</t>
+    <t xml:space="preserve">【背景】
+心房細動（AF）カテーテルアブレーション後のブランキング期間中における早期再発（ER）は頻見されるが、ER の発生時期の違い（発症タイミングの変動）が長期的な晩期再発（LR）および潜在的な不整脈基質とどのように関連しているかは解明されていない。
+【方法】
+AFACT 試験および MARK-AF レジストリに登録されたアブレーション施行 AF 患者449例を対象とし、ブランキング期間中の ER 発症時期を「初期（1ヶ月目）」「中期（2ヶ月目）」「後期（3ヶ月目）」に分類。長期追跡における AF 晩期再発率との相関を連続モニタリングにより評価した。
+【結果】
+ブランキング期間の後期（2〜3ヶ月目）に認められた遅発性の早期再発は、初期の早期再発と比較して晩期再発リスクが著しく高かった（ハザード比 3.42; 95% CI: 2.15〜5.44; P &lt; 0.001）。これは一過性の炎症反応を超えた不可逆的な心筋不整脈基質の残存を反映している。
+【結論】
+アブレーション後の早期再発における発生タイミングは臨床予後と強く相関しており、特にブランキング期間後期の早期再発は長期再発の強力な独立予測因子であり、再治療の必要性を示唆する。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -5117,7 +5131,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -5221,7 +5235,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -8710,7 +8724,7 @@
       </c>
       <c r="B16" s="25"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>478</v>
       </c>
@@ -17818,7 +17832,7 @@
       </c>
       <c r="B16" s="25"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>527</v>
       </c>
